--- a/relatorio_vendas_margens_2026-07-18_2026-08-17.xlsx
+++ b/relatorio_vendas_margens_2026-07-18_2026-08-17.xlsx
@@ -441,7 +441,7 @@
         <v>17/08/2026</v>
       </c>
       <c r="B2" t="str">
-        <v>19:58</v>
+        <v>20:06</v>
       </c>
       <c r="C2" t="str">
         <v>Test Store</v>

--- a/relatorio_vendas_margens_2026-07-18_2026-08-17.xlsx
+++ b/relatorio_vendas_margens_2026-07-18_2026-08-17.xlsx
@@ -441,7 +441,7 @@
         <v>17/08/2026</v>
       </c>
       <c r="B2" t="str">
-        <v>20:06</v>
+        <v>20:07</v>
       </c>
       <c r="C2" t="str">
         <v>Test Store</v>

--- a/relatorio_vendas_margens_2026-07-18_2026-08-17.xlsx
+++ b/relatorio_vendas_margens_2026-07-18_2026-08-17.xlsx
@@ -441,7 +441,7 @@
         <v>17/08/2026</v>
       </c>
       <c r="B2" t="str">
-        <v>20:07</v>
+        <v>20:08</v>
       </c>
       <c r="C2" t="str">
         <v>Test Store</v>
